--- a/public/templates/examples/A-070-AccessAuthorizationList-EXAMPLE-M.xlsx
+++ b/public/templates/examples/A-070-AccessAuthorizationList-EXAMPLE-M.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="0"/>
   <fonts count="6">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -251,12 +251,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="876300" cy="876300"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -395,7 +395,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -429,7 +429,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/examples/A-070-AccessAuthorizationList-EXAMPLE-M.xlsx
+++ b/public/templates/examples/A-070-AccessAuthorizationList-EXAMPLE-M.xlsx
@@ -4,19 +4,21 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Aptos"/>
@@ -143,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -169,6 +171,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -786,7 +791,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>ID</t>
@@ -864,10 +869,8 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
+      <c r="F12" s="11">
+        <v>45901</v>
       </c>
       <c r="G12" s="8" t="inlineStr"/>
       <c r="H12" s="8" t="inlineStr">
@@ -875,18 +878,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+      <c r="I12" s="11">
+        <v>46082</v>
+      </c>
+      <c r="J12" s="11">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>AUTH-002</t>
@@ -912,10 +911,8 @@
           <t>Facilities Coordinator</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
+      <c r="F13" s="11">
+        <v>45901</v>
       </c>
       <c r="G13" s="8" t="inlineStr"/>
       <c r="H13" s="8" t="inlineStr">
@@ -923,18 +920,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
+      <c r="I13" s="11">
+        <v>46082</v>
+      </c>
+      <c r="J13" s="11">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>AUTH-003</t>
@@ -960,10 +953,8 @@
           <t>Facilities Coordinator</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
+      <c r="F14" s="11">
+        <v>45901</v>
       </c>
       <c r="G14" s="8" t="inlineStr"/>
       <c r="H14" s="8" t="inlineStr">
@@ -971,18 +962,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+      <c r="I14" s="11">
+        <v>46082</v>
+      </c>
+      <c r="J14" s="11">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="15" ht="34.7" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>AUTH-004</t>
@@ -1008,10 +995,8 @@
           <t>Facilities Coordinator</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
+      <c r="F15" s="11">
+        <v>45901</v>
       </c>
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="8" t="inlineStr">
@@ -1019,18 +1004,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
+      <c r="I15" s="11">
+        <v>46082</v>
+      </c>
+      <c r="J15" s="11">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>AUTH-005</t>
@@ -1056,29 +1037,23 @@
           <t>Facilities Coordinator</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
+      <c r="F16" s="11">
+        <v>46063</v>
+      </c>
+      <c r="G16" s="11">
+        <v>46063</v>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Revoked</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
+      <c r="I16" s="11">
+        <v>46063</v>
       </c>
       <c r="J16" s="8" t="inlineStr"/>
     </row>
-    <row r="17">
+    <row r="17" ht="34.7" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>AUTH-006</t>
@@ -1104,36 +1079,30 @@
           <t>Facilities Coordinator</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>2024-07-01</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
+      <c r="F17" s="11">
+        <v>45474</v>
+      </c>
+      <c r="G17" s="11">
+        <v>46042</v>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Revoked</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
+      <c r="I17" s="11">
+        <v>46042</v>
       </c>
       <c r="J17" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+          <t>Summary (as of 2026-04-24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34.7" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Total entries</t>
@@ -1141,7 +1110,6 @@
       </c>
       <c r="C20" s="10">
         <f>COUNTA(A12:A17)</f>
-        <v/>
       </c>
     </row>
     <row r="21">
@@ -1152,10 +1120,9 @@
       </c>
       <c r="C21" s="10">
         <f>COUNTIF(H12:H17,"Active")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
+      </c>
+    </row>
+    <row r="22" ht="34.7" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Suspended</t>
@@ -1163,7 +1130,6 @@
       </c>
       <c r="C22" s="10">
         <f>COUNTIF(H12:H17,"Suspended")</f>
-        <v/>
       </c>
     </row>
     <row r="23">
@@ -1174,18 +1140,16 @@
       </c>
       <c r="C23" s="10">
         <f>COUNTIF(H12:H17,"Revoked")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
+      </c>
+    </row>
+    <row r="24" ht="34.7" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Past due for review</t>
         </is>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIF(J12:J17,"&lt;"&amp;TODAY())</f>
-        <v/>
+        <f>COUNTIF(J12:J17,"&lt;"&amp;DATE(2026,4,24))</f>
       </c>
     </row>
     <row r="26">
@@ -1268,13 +1232,11 @@
           <t>Anthony Reyes</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
+      <c r="D34" s="11">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="35" ht="34.7" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>Facilities Coordinator</t>
@@ -1290,10 +1252,8 @@
           <t>(on file)</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
+      <c r="D35" s="11">
+        <v>46083</v>
       </c>
     </row>
     <row r="37">
@@ -1325,16 +1285,14 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="34.7" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
+      <c r="B39" s="11">
+        <v>46083</v>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
@@ -1371,8 +1329,8 @@
     <mergeCell ref="A26:J26"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>